--- a/Gearbox_DaughterBoard/BOM DBB.xlsx
+++ b/Gearbox_DaughterBoard/BOM DBB.xlsx
@@ -52,16 +52,16 @@
     <t>C2,C3</t>
   </si>
   <si>
-    <t>C0603</t>
-  </si>
-  <si>
-    <t>CC0603KRX7R9BB104</t>
-  </si>
-  <si>
-    <t>YAGEO(国巨)</t>
-  </si>
-  <si>
-    <t>C14663</t>
+    <t>C0402</t>
+  </si>
+  <si>
+    <t>CL05B104KB54PNC</t>
+  </si>
+  <si>
+    <t>SAMSUNG(三星)</t>
+  </si>
+  <si>
+    <t>C307331</t>
   </si>
   <si>
     <t>LCSC</t>
@@ -70,22 +70,22 @@
     <t>2</t>
   </si>
   <si>
-    <t>SH1.0mm-2P-LT</t>
+    <t>S2B-ZR-SM2-TF(LF)(SN)</t>
   </si>
   <si>
     <t>CN6,CN9,CN10,CN11</t>
   </si>
   <si>
-    <t>CONN-SMD_SH1.0MM-2P-LT</t>
+    <t>CONN-SMD_2P-P1.50_S2B-ZR-SM2-TF-LF-SN</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>LXWCONN(连兴旺电子)</t>
-  </si>
-  <si>
-    <t>C53055327</t>
+    <t>JST</t>
+  </si>
+  <si>
+    <t>C5306678</t>
   </si>
   <si>
     <t>3</t>
@@ -115,16 +115,16 @@
     <t>R2,R3</t>
   </si>
   <si>
-    <t>R0603</t>
-  </si>
-  <si>
-    <t>FRC0603J102 TS</t>
-  </si>
-  <si>
-    <t>FOJAN(富捷)</t>
-  </si>
-  <si>
-    <t>C2907113</t>
+    <t>R0402</t>
+  </si>
+  <si>
+    <t>0402WGF1001TCE</t>
+  </si>
+  <si>
+    <t>UNI-ROYAL(厚声)</t>
+  </si>
+  <si>
+    <t>C11702</t>
   </si>
   <si>
     <t>5</t>
